--- a/data/trans_dic/P32E$eventos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,51</t>
+          <t>0,0; 59,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 25,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,07</t>
+          <t>0,0; 47,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,39</t>
+          <t>0,0; 20,38</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,2</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,52</t>
+          <t>0,0; 19,54</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,22</t>
+          <t>0,0; 27,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 29,2</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,46</t>
+          <t>0,58; 5,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 21,94</t>
+          <t>2,17; 22,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,78</t>
+          <t>1,63; 8,08</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9137</t>
+          <t>0; 9197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9693</t>
+          <t>0; 10247</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 6438</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7079</t>
+          <t>0; 7439</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1828</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1713</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6952</t>
+          <t>0; 6968</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6416</t>
+          <t>0; 7157</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1546</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1412</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>0; 3674</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 809</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3735</t>
+          <t>0; 4885</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1056</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1166</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>897; 9310</t>
+          <t>831; 8005</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1634; 12007</t>
+          <t>1189; 12378</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3600; 15474</t>
+          <t>3232; 16067</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$eventos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,91</t>
+          <t>0,0; 49,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,0</t>
+          <t>0,0; 18,27</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,55</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,38</t>
+          <t>0,0; 17,9</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>0,0; 19,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,54</t>
+          <t>0,0; 17,88</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,73</t>
+          <t>0,0; 31,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,2</t>
+          <t>0,0; 28,77</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,56</t>
+          <t>0,55; 4,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 22,62</t>
+          <t>2,55; 19,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,08</t>
+          <t>1,71; 7,26</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2651</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9197</t>
+          <t>0; 8895</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 10247</t>
+          <t>0; 8680</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6438</t>
+          <t>0; 6670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7439</t>
+          <t>0; 7855</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6968</t>
+          <t>0; 6018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7157</t>
+          <t>0; 7366</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3674</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4885</t>
+          <t>0; 5271</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>831; 8005</t>
+          <t>880; 7733</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1189; 12378</t>
+          <t>1638; 12261</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3232; 16067</t>
+          <t>3861; 16381</t>
         </is>
       </c>
     </row>
